--- a/pds_admin_raj/Backend/Backend/Tagging_Sheet_Pre.xlsx
+++ b/pds_admin_raj/Backend/Backend/Tagging_Sheet_Pre.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3462" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3462" uniqueCount="456">
   <si>
     <t>Var</t>
   </si>
@@ -580,561 +580,555 @@
     <t>17520.0</t>
   </si>
   <si>
+    <t>22540.0</t>
+  </si>
+  <si>
+    <t>60200.0</t>
+  </si>
+  <si>
+    <t>30070.0</t>
+  </si>
+  <si>
+    <t>18298.0</t>
+  </si>
+  <si>
+    <t>15200.0</t>
+  </si>
+  <si>
+    <t>67200.0</t>
+  </si>
+  <si>
+    <t>38120.0</t>
+  </si>
+  <si>
+    <t>78400.0</t>
+  </si>
+  <si>
+    <t>7509.0</t>
+  </si>
+  <si>
+    <t>9530.0</t>
+  </si>
+  <si>
+    <t>55350.0</t>
+  </si>
+  <si>
+    <t>35550.0</t>
+  </si>
+  <si>
+    <t>59878.0</t>
+  </si>
+  <si>
+    <t>72800.0</t>
+  </si>
+  <si>
+    <t>43400.0</t>
+  </si>
+  <si>
+    <t>1962.0</t>
+  </si>
+  <si>
+    <t>44800.0</t>
+  </si>
+  <si>
+    <t>128070.0</t>
+  </si>
+  <si>
+    <t>85460.0</t>
+  </si>
+  <si>
+    <t>2152.5</t>
+  </si>
+  <si>
+    <t>63400.0</t>
+  </si>
+  <si>
+    <t>19870.0</t>
+  </si>
+  <si>
+    <t>50400.0</t>
+  </si>
+  <si>
+    <t>71000.0</t>
+  </si>
+  <si>
+    <t>13730.0</t>
+  </si>
+  <si>
+    <t>28000.0</t>
+  </si>
+  <si>
+    <t>71870.0</t>
+  </si>
+  <si>
+    <t>30590.0</t>
+  </si>
+  <si>
+    <t>36690.0</t>
+  </si>
+  <si>
+    <t>110830.0</t>
+  </si>
+  <si>
+    <t>52740.0</t>
+  </si>
+  <si>
+    <t>13710.0</t>
+  </si>
+  <si>
+    <t>17710.0</t>
+  </si>
+  <si>
+    <t>97700.0</t>
+  </si>
+  <si>
+    <t>31110.0</t>
+  </si>
+  <si>
+    <t>20590.0</t>
+  </si>
+  <si>
+    <t>4728.97</t>
+  </si>
+  <si>
+    <t>27231.03</t>
+  </si>
+  <si>
+    <t>3053.33</t>
+  </si>
+  <si>
+    <t>15206.67</t>
+  </si>
+  <si>
+    <t>32708.97</t>
+  </si>
+  <si>
+    <t>4738.97</t>
+  </si>
+  <si>
+    <t>4391.03</t>
+  </si>
+  <si>
+    <t>5501.3</t>
+  </si>
+  <si>
+    <t>4228.7</t>
+  </si>
+  <si>
+    <t>8530.0</t>
+  </si>
+  <si>
+    <t>27720.0</t>
+  </si>
+  <si>
+    <t>66100.0</t>
+  </si>
+  <si>
+    <t>20000.0</t>
+  </si>
+  <si>
+    <t>4270.0</t>
+  </si>
+  <si>
+    <t>35730.0</t>
+  </si>
+  <si>
+    <t>12850.0</t>
+  </si>
+  <si>
+    <t>46410.0</t>
+  </si>
+  <si>
+    <t>44890.0</t>
+  </si>
+  <si>
+    <t>17561.0</t>
+  </si>
+  <si>
+    <t>9829.0</t>
+  </si>
+  <si>
+    <t>13830.2</t>
+  </si>
+  <si>
+    <t>4429.8</t>
+  </si>
+  <si>
+    <t>120599.8</t>
+  </si>
+  <si>
+    <t>153557.0</t>
+  </si>
+  <si>
+    <t>38286.0</t>
+  </si>
+  <si>
+    <t>38521.5</t>
+  </si>
+  <si>
+    <t>14855.7</t>
+  </si>
+  <si>
+    <t>2027.66</t>
+  </si>
+  <si>
+    <t>16232.34</t>
+  </si>
+  <si>
+    <t>18040.0</t>
+  </si>
+  <si>
+    <t>220.0</t>
+  </si>
+  <si>
+    <t>8390.0</t>
+  </si>
+  <si>
+    <t>9870.0</t>
+  </si>
+  <si>
+    <t>16400.93</t>
+  </si>
+  <si>
+    <t>6429.07</t>
+  </si>
+  <si>
+    <t>28520.0</t>
+  </si>
+  <si>
+    <t>17390.2</t>
+  </si>
+  <si>
+    <t>9999.8</t>
+  </si>
+  <si>
+    <t>8459.0</t>
+  </si>
+  <si>
+    <t>671.0</t>
+  </si>
+  <si>
+    <t>3230.0</t>
+  </si>
+  <si>
+    <t>42310.2</t>
+  </si>
+  <si>
+    <t>4598.69</t>
+  </si>
+  <si>
+    <t>7871.11</t>
+  </si>
+  <si>
+    <t>16470.0</t>
+  </si>
+  <si>
+    <t>6360.0</t>
+  </si>
+  <si>
+    <t>32851.16</t>
+  </si>
+  <si>
+    <t>15000.0</t>
+  </si>
+  <si>
+    <t>4335.54</t>
+  </si>
+  <si>
+    <t>55192.3</t>
+  </si>
+  <si>
+    <t>7921.0</t>
+  </si>
+  <si>
+    <t>3400.0</t>
+  </si>
+  <si>
+    <t>14939.0</t>
+  </si>
+  <si>
+    <t>3321.0</t>
+  </si>
+  <si>
+    <t>33661.0</t>
+  </si>
+  <si>
+    <t>57639.0</t>
+  </si>
+  <si>
+    <t>11090.0</t>
+  </si>
+  <si>
+    <t>65100.0</t>
+  </si>
+  <si>
+    <t>42700.0</t>
+  </si>
+  <si>
+    <t>64473.0</t>
+  </si>
+  <si>
+    <t>51750.0</t>
+  </si>
+  <si>
+    <t>29400.0</t>
+  </si>
+  <si>
+    <t>14270.0</t>
+  </si>
+  <si>
+    <t>22700.0</t>
+  </si>
+  <si>
+    <t>58910.0</t>
+  </si>
+  <si>
+    <t>5170.0</t>
+  </si>
+  <si>
+    <t>63950.0</t>
+  </si>
+  <si>
+    <t>52400.0</t>
+  </si>
+  <si>
+    <t>3350.0</t>
+  </si>
+  <si>
+    <t>30450.0</t>
+  </si>
+  <si>
+    <t>26190.0</t>
+  </si>
+  <si>
+    <t>42830.0</t>
+  </si>
+  <si>
+    <t>36400.0</t>
+  </si>
+  <si>
+    <t>37010.0</t>
+  </si>
+  <si>
+    <t>102420.0</t>
+  </si>
+  <si>
+    <t>10300.0</t>
+  </si>
+  <si>
+    <t>660.0</t>
+  </si>
+  <si>
+    <t>40400.0</t>
+  </si>
+  <si>
+    <t>58800.0</t>
+  </si>
+  <si>
+    <t>51600.0</t>
+  </si>
+  <si>
+    <t>44500.0</t>
+  </si>
+  <si>
+    <t>138110.0</t>
+  </si>
+  <si>
+    <t>18589.0</t>
+  </si>
+  <si>
+    <t>32430.0</t>
+  </si>
+  <si>
+    <t>40281.0</t>
+  </si>
+  <si>
+    <t>54339.86</t>
+  </si>
+  <si>
+    <t>3040.0</t>
+  </si>
+  <si>
+    <t>33700.0</t>
+  </si>
+  <si>
+    <t>74870.0</t>
+  </si>
+  <si>
+    <t>84450.0</t>
+  </si>
+  <si>
+    <t>54139.0</t>
+  </si>
+  <si>
+    <t>9771.0</t>
+  </si>
+  <si>
+    <t>71700.0</t>
+  </si>
+  <si>
+    <t>56640.0</t>
+  </si>
+  <si>
+    <t>74700.0</t>
+  </si>
+  <si>
+    <t>144014.5</t>
+  </si>
+  <si>
+    <t>51285.5</t>
+  </si>
+  <si>
+    <t>88500.0</t>
+  </si>
+  <si>
+    <t>33684.5</t>
+  </si>
+  <si>
+    <t>81500.0</t>
+  </si>
+  <si>
+    <t>40300.0</t>
+  </si>
+  <si>
+    <t>61600.0</t>
+  </si>
+  <si>
+    <t>4960.0</t>
+  </si>
+  <si>
+    <t>58700.0</t>
+  </si>
+  <si>
+    <t>69200.0</t>
+  </si>
+  <si>
+    <t>30680.0</t>
+  </si>
+  <si>
+    <t>34500.0</t>
+  </si>
+  <si>
+    <t>2920.0</t>
+  </si>
+  <si>
+    <t>21780.0</t>
+  </si>
+  <si>
+    <t>21480.0</t>
+  </si>
+  <si>
+    <t>20249.28</t>
+  </si>
+  <si>
+    <t>24722.86</t>
+  </si>
+  <si>
+    <t>13420.0</t>
+  </si>
+  <si>
+    <t>4840.0</t>
+  </si>
+  <si>
+    <t>11701.0</t>
+  </si>
+  <si>
+    <t>6559.0</t>
+  </si>
+  <si>
+    <t>25277.14</t>
+  </si>
+  <si>
+    <t>2112.86</t>
+  </si>
+  <si>
+    <t>6833.26</t>
+  </si>
+  <si>
+    <t>16207.36</t>
+  </si>
+  <si>
+    <t>11182.64</t>
+  </si>
+  <si>
+    <t>97450.0</t>
+  </si>
+  <si>
+    <t>8890.0</t>
+  </si>
+  <si>
+    <t>18500.0</t>
+  </si>
+  <si>
+    <t>18000.0</t>
+  </si>
+  <si>
+    <t>18637.0</t>
+  </si>
+  <si>
+    <t>30550.0</t>
+  </si>
+  <si>
+    <t>11570.0</t>
+  </si>
+  <si>
+    <t>36270.0</t>
+  </si>
+  <si>
+    <t>40000.0</t>
+  </si>
+  <si>
+    <t>30250.0</t>
+  </si>
+  <si>
+    <t>17340.0</t>
+  </si>
+  <si>
+    <t>14380.0</t>
+  </si>
+  <si>
+    <t>30000.0</t>
+  </si>
+  <si>
+    <t>48000.0</t>
+  </si>
+  <si>
+    <t>71389.14</t>
+  </si>
+  <si>
+    <t>69270.0</t>
+  </si>
+  <si>
+    <t>10720.86</t>
+  </si>
+  <si>
+    <t>50000.0</t>
+  </si>
+  <si>
+    <t>20880.0</t>
+  </si>
+  <si>
+    <t>31320.0</t>
+  </si>
+  <si>
+    <t>26278.36</t>
+  </si>
+  <si>
+    <t>27000.0</t>
+  </si>
+  <si>
+    <t>30190.0</t>
+  </si>
+  <si>
+    <t>113731.64</t>
+  </si>
+  <si>
+    <t>11810.0</t>
+  </si>
+  <si>
     <t>37740.0</t>
   </si>
   <si>
-    <t>45000.0</t>
-  </si>
-  <si>
-    <t>30070.0</t>
-  </si>
-  <si>
-    <t>18298.0</t>
-  </si>
-  <si>
-    <t>22200.0</t>
-  </si>
-  <si>
-    <t>60200.0</t>
-  </si>
-  <si>
-    <t>38120.0</t>
-  </si>
-  <si>
-    <t>67200.0</t>
-  </si>
-  <si>
-    <t>78400.0</t>
-  </si>
-  <si>
-    <t>7509.0</t>
-  </si>
-  <si>
-    <t>9530.0</t>
-  </si>
-  <si>
-    <t>55350.0</t>
-  </si>
-  <si>
-    <t>35550.0</t>
-  </si>
-  <si>
-    <t>15665.5</t>
-  </si>
-  <si>
-    <t>72800.0</t>
-  </si>
-  <si>
-    <t>89574.5</t>
-  </si>
-  <si>
-    <t>42647.5</t>
-  </si>
-  <si>
-    <t>44800.0</t>
-  </si>
-  <si>
-    <t>128070.0</t>
-  </si>
-  <si>
-    <t>44212.5</t>
-  </si>
-  <si>
-    <t>43400.0</t>
-  </si>
-  <si>
-    <t>2152.5</t>
-  </si>
-  <si>
-    <t>63400.0</t>
-  </si>
-  <si>
-    <t>19870.0</t>
-  </si>
-  <si>
-    <t>50400.0</t>
-  </si>
-  <si>
-    <t>71000.0</t>
-  </si>
-  <si>
-    <t>13730.0</t>
-  </si>
-  <si>
-    <t>28000.0</t>
-  </si>
-  <si>
-    <t>71870.0</t>
-  </si>
-  <si>
-    <t>30590.0</t>
-  </si>
-  <si>
-    <t>36690.0</t>
-  </si>
-  <si>
-    <t>110830.0</t>
-  </si>
-  <si>
-    <t>52740.0</t>
-  </si>
-  <si>
-    <t>13710.0</t>
-  </si>
-  <si>
-    <t>48820.0</t>
-  </si>
-  <si>
-    <t>97700.0</t>
-  </si>
-  <si>
-    <t>36090.0</t>
-  </si>
-  <si>
-    <t>31110.0</t>
-  </si>
-  <si>
-    <t>20590.0</t>
-  </si>
-  <si>
-    <t>4728.97</t>
-  </si>
-  <si>
-    <t>27231.03</t>
-  </si>
-  <si>
-    <t>3053.33</t>
-  </si>
-  <si>
-    <t>15206.67</t>
-  </si>
-  <si>
-    <t>32708.97</t>
-  </si>
-  <si>
-    <t>4738.97</t>
-  </si>
-  <si>
-    <t>4391.03</t>
-  </si>
-  <si>
-    <t>5501.3</t>
-  </si>
-  <si>
-    <t>4228.7</t>
-  </si>
-  <si>
-    <t>8530.0</t>
-  </si>
-  <si>
-    <t>27720.0</t>
-  </si>
-  <si>
-    <t>66100.0</t>
-  </si>
-  <si>
-    <t>20000.0</t>
-  </si>
-  <si>
-    <t>4270.0</t>
-  </si>
-  <si>
-    <t>35730.0</t>
-  </si>
-  <si>
-    <t>12850.0</t>
-  </si>
-  <si>
-    <t>46410.0</t>
-  </si>
-  <si>
-    <t>44890.0</t>
-  </si>
-  <si>
-    <t>17561.0</t>
-  </si>
-  <si>
-    <t>9829.0</t>
-  </si>
-  <si>
-    <t>13830.2</t>
-  </si>
-  <si>
-    <t>4429.8</t>
-  </si>
-  <si>
-    <t>120599.8</t>
-  </si>
-  <si>
-    <t>153557.0</t>
-  </si>
-  <si>
-    <t>38286.0</t>
-  </si>
-  <si>
-    <t>38521.5</t>
-  </si>
-  <si>
-    <t>14855.7</t>
-  </si>
-  <si>
-    <t>2027.66</t>
-  </si>
-  <si>
-    <t>16232.34</t>
-  </si>
-  <si>
-    <t>18040.0</t>
-  </si>
-  <si>
-    <t>220.0</t>
-  </si>
-  <si>
-    <t>8390.0</t>
-  </si>
-  <si>
-    <t>9870.0</t>
-  </si>
-  <si>
-    <t>16400.93</t>
-  </si>
-  <si>
-    <t>6429.07</t>
-  </si>
-  <si>
-    <t>17390.2</t>
-  </si>
-  <si>
-    <t>11129.8</t>
-  </si>
-  <si>
-    <t>8459.0</t>
-  </si>
-  <si>
-    <t>671.0</t>
-  </si>
-  <si>
-    <t>3230.0</t>
-  </si>
-  <si>
-    <t>42310.2</t>
-  </si>
-  <si>
-    <t>4598.69</t>
-  </si>
-  <si>
-    <t>7871.11</t>
-  </si>
-  <si>
-    <t>16470.0</t>
-  </si>
-  <si>
-    <t>6360.0</t>
-  </si>
-  <si>
-    <t>32851.16</t>
-  </si>
-  <si>
-    <t>15000.0</t>
-  </si>
-  <si>
-    <t>4335.54</t>
-  </si>
-  <si>
-    <t>55192.3</t>
-  </si>
-  <si>
-    <t>7921.0</t>
-  </si>
-  <si>
-    <t>3400.0</t>
-  </si>
-  <si>
-    <t>14939.0</t>
-  </si>
-  <si>
-    <t>3321.0</t>
-  </si>
-  <si>
-    <t>33661.0</t>
-  </si>
-  <si>
-    <t>57639.0</t>
-  </si>
-  <si>
-    <t>11090.0</t>
-  </si>
-  <si>
-    <t>65100.0</t>
-  </si>
-  <si>
-    <t>42700.0</t>
-  </si>
-  <si>
-    <t>64473.0</t>
-  </si>
-  <si>
-    <t>51750.0</t>
-  </si>
-  <si>
-    <t>29400.0</t>
-  </si>
-  <si>
-    <t>14270.0</t>
-  </si>
-  <si>
-    <t>22700.0</t>
-  </si>
-  <si>
-    <t>58910.0</t>
-  </si>
-  <si>
-    <t>5170.0</t>
-  </si>
-  <si>
-    <t>63950.0</t>
-  </si>
-  <si>
-    <t>52400.0</t>
-  </si>
-  <si>
-    <t>3350.0</t>
-  </si>
-  <si>
-    <t>30450.0</t>
-  </si>
-  <si>
-    <t>26190.0</t>
-  </si>
-  <si>
-    <t>42830.0</t>
-  </si>
-  <si>
-    <t>36400.0</t>
-  </si>
-  <si>
-    <t>37010.0</t>
-  </si>
-  <si>
-    <t>7790.0</t>
-  </si>
-  <si>
-    <t>102420.0</t>
-  </si>
-  <si>
-    <t>10300.0</t>
-  </si>
-  <si>
-    <t>660.0</t>
-  </si>
-  <si>
-    <t>40400.0</t>
-  </si>
-  <si>
-    <t>58800.0</t>
-  </si>
-  <si>
-    <t>51600.0</t>
-  </si>
-  <si>
-    <t>44500.0</t>
-  </si>
-  <si>
-    <t>138110.0</t>
-  </si>
-  <si>
-    <t>18589.0</t>
-  </si>
-  <si>
-    <t>32430.0</t>
-  </si>
-  <si>
-    <t>40281.0</t>
-  </si>
-  <si>
-    <t>54339.86</t>
-  </si>
-  <si>
-    <t>3040.0</t>
-  </si>
-  <si>
-    <t>33700.0</t>
-  </si>
-  <si>
-    <t>74870.0</t>
-  </si>
-  <si>
-    <t>84450.0</t>
-  </si>
-  <si>
-    <t>54139.0</t>
-  </si>
-  <si>
-    <t>9771.0</t>
-  </si>
-  <si>
-    <t>71700.0</t>
-  </si>
-  <si>
-    <t>56640.0</t>
-  </si>
-  <si>
-    <t>74700.0</t>
-  </si>
-  <si>
-    <t>144014.5</t>
-  </si>
-  <si>
-    <t>51285.5</t>
-  </si>
-  <si>
-    <t>88500.0</t>
-  </si>
-  <si>
-    <t>33684.5</t>
-  </si>
-  <si>
-    <t>81500.0</t>
-  </si>
-  <si>
-    <t>40300.0</t>
-  </si>
-  <si>
-    <t>61600.0</t>
-  </si>
-  <si>
-    <t>4960.0</t>
-  </si>
-  <si>
-    <t>58700.0</t>
-  </si>
-  <si>
-    <t>69200.0</t>
-  </si>
-  <si>
-    <t>30680.0</t>
-  </si>
-  <si>
-    <t>34500.0</t>
-  </si>
-  <si>
-    <t>2920.0</t>
-  </si>
-  <si>
-    <t>21780.0</t>
-  </si>
-  <si>
-    <t>21480.0</t>
-  </si>
-  <si>
-    <t>20249.28</t>
-  </si>
-  <si>
-    <t>24722.86</t>
-  </si>
-  <si>
-    <t>13420.0</t>
-  </si>
-  <si>
-    <t>4840.0</t>
-  </si>
-  <si>
-    <t>11701.0</t>
-  </si>
-  <si>
-    <t>6559.0</t>
-  </si>
-  <si>
-    <t>25277.14</t>
-  </si>
-  <si>
-    <t>2112.86</t>
-  </si>
-  <si>
-    <t>6833.26</t>
-  </si>
-  <si>
-    <t>16207.36</t>
-  </si>
-  <si>
-    <t>11182.64</t>
-  </si>
-  <si>
-    <t>97450.0</t>
-  </si>
-  <si>
-    <t>8890.0</t>
-  </si>
-  <si>
-    <t>18500.0</t>
-  </si>
-  <si>
-    <t>18000.0</t>
-  </si>
-  <si>
-    <t>18637.0</t>
-  </si>
-  <si>
-    <t>30550.0</t>
-  </si>
-  <si>
-    <t>11570.0</t>
-  </si>
-  <si>
-    <t>36270.0</t>
-  </si>
-  <si>
-    <t>40000.0</t>
-  </si>
-  <si>
-    <t>30250.0</t>
-  </si>
-  <si>
-    <t>17340.0</t>
-  </si>
-  <si>
-    <t>14380.0</t>
-  </si>
-  <si>
-    <t>30000.0</t>
-  </si>
-  <si>
-    <t>48000.0</t>
-  </si>
-  <si>
-    <t>71389.14</t>
-  </si>
-  <si>
-    <t>69270.0</t>
-  </si>
-  <si>
-    <t>10720.86</t>
-  </si>
-  <si>
-    <t>50000.0</t>
-  </si>
-  <si>
-    <t>20880.0</t>
-  </si>
-  <si>
-    <t>31320.0</t>
-  </si>
-  <si>
-    <t>26278.36</t>
-  </si>
-  <si>
-    <t>27000.0</t>
-  </si>
-  <si>
-    <t>30190.0</t>
-  </si>
-  <si>
-    <t>113731.64</t>
-  </si>
-  <si>
-    <t>11810.0</t>
-  </si>
-  <si>
     <t>30980.0</t>
   </si>
   <si>
@@ -1225,13 +1219,13 @@
     <t>93097.0</t>
   </si>
   <si>
-    <t>14997.0</t>
+    <t>73400.0</t>
   </si>
   <si>
     <t>36743.0</t>
   </si>
   <si>
-    <t>80470.0</t>
+    <t>22067.0</t>
   </si>
   <si>
     <t>15930.0</t>
@@ -8545,7 +8539,7 @@
         <v>18</v>
       </c>
       <c r="E262">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -8623,7 +8617,7 @@
         <v>18</v>
       </c>
       <c r="E265">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -8649,7 +8643,7 @@
         <v>18</v>
       </c>
       <c r="E266">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -8710,7 +8704,7 @@
         <v>59</v>
       </c>
       <c r="H268" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -8736,7 +8730,7 @@
         <v>59</v>
       </c>
       <c r="H269" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -8814,7 +8808,7 @@
         <v>66</v>
       </c>
       <c r="H272" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -8840,7 +8834,7 @@
         <v>59</v>
       </c>
       <c r="H273" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -8866,7 +8860,7 @@
         <v>59</v>
       </c>
       <c r="H274" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -8892,7 +8886,7 @@
         <v>59</v>
       </c>
       <c r="H275" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -8944,7 +8938,7 @@
         <v>59</v>
       </c>
       <c r="H277" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -8970,7 +8964,7 @@
         <v>59</v>
       </c>
       <c r="H278" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -8987,7 +8981,7 @@
         <v>18</v>
       </c>
       <c r="E279">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F279" t="s">
         <v>18</v>
@@ -8996,7 +8990,7 @@
         <v>59</v>
       </c>
       <c r="H279" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9007,13 +9001,13 @@
         <v>7</v>
       </c>
       <c r="C280">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D280" t="s">
         <v>18</v>
       </c>
       <c r="E280">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="F280" t="s">
         <v>18</v>
@@ -9022,7 +9016,7 @@
         <v>59</v>
       </c>
       <c r="H280" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -9039,7 +9033,7 @@
         <v>18</v>
       </c>
       <c r="E281">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F281" t="s">
         <v>18</v>
@@ -9048,7 +9042,7 @@
         <v>59</v>
       </c>
       <c r="H281" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -9065,7 +9059,7 @@
         <v>18</v>
       </c>
       <c r="E282">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F282" t="s">
         <v>18</v>
@@ -9074,7 +9068,7 @@
         <v>59</v>
       </c>
       <c r="H282" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -9091,7 +9085,7 @@
         <v>18</v>
       </c>
       <c r="E283">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="F283" t="s">
         <v>18</v>
@@ -9100,7 +9094,7 @@
         <v>59</v>
       </c>
       <c r="H283" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9117,7 +9111,7 @@
         <v>18</v>
       </c>
       <c r="E284">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F284" t="s">
         <v>18</v>
@@ -9126,7 +9120,7 @@
         <v>59</v>
       </c>
       <c r="H284" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -9143,7 +9137,7 @@
         <v>18</v>
       </c>
       <c r="E285">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="F285" t="s">
         <v>18</v>
@@ -9152,7 +9146,7 @@
         <v>59</v>
       </c>
       <c r="H285" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -9204,7 +9198,7 @@
         <v>59</v>
       </c>
       <c r="H287" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -9230,7 +9224,7 @@
         <v>59</v>
       </c>
       <c r="H288" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -9256,7 +9250,7 @@
         <v>59</v>
       </c>
       <c r="H289" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -9282,7 +9276,7 @@
         <v>59</v>
       </c>
       <c r="H290" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -9308,7 +9302,7 @@
         <v>59</v>
       </c>
       <c r="H291" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -9334,7 +9328,7 @@
         <v>59</v>
       </c>
       <c r="H292" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -9360,7 +9354,7 @@
         <v>59</v>
       </c>
       <c r="H293" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -9386,7 +9380,7 @@
         <v>59</v>
       </c>
       <c r="H294" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -9412,7 +9406,7 @@
         <v>59</v>
       </c>
       <c r="H295" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -9464,7 +9458,7 @@
         <v>59</v>
       </c>
       <c r="H297" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -9490,7 +9484,7 @@
         <v>59</v>
       </c>
       <c r="H298" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -9516,7 +9510,7 @@
         <v>59</v>
       </c>
       <c r="H299" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -9542,7 +9536,7 @@
         <v>59</v>
       </c>
       <c r="H300" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -9568,7 +9562,7 @@
         <v>59</v>
       </c>
       <c r="H301" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -9620,7 +9614,7 @@
         <v>59</v>
       </c>
       <c r="H303" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -9646,7 +9640,7 @@
         <v>59</v>
       </c>
       <c r="H304" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -9672,7 +9666,7 @@
         <v>59</v>
       </c>
       <c r="H305" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -9689,7 +9683,7 @@
         <v>18</v>
       </c>
       <c r="E306">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="F306" t="s">
         <v>18</v>
@@ -9698,7 +9692,7 @@
         <v>59</v>
       </c>
       <c r="H306" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -9724,7 +9718,7 @@
         <v>59</v>
       </c>
       <c r="H307" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -9776,7 +9770,7 @@
         <v>59</v>
       </c>
       <c r="H309" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -9802,7 +9796,7 @@
         <v>59</v>
       </c>
       <c r="H310" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -9854,7 +9848,7 @@
         <v>59</v>
       </c>
       <c r="H312" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -9880,7 +9874,7 @@
         <v>59</v>
       </c>
       <c r="H313" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -9906,7 +9900,7 @@
         <v>59</v>
       </c>
       <c r="H314" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10114,7 +10108,7 @@
         <v>59</v>
       </c>
       <c r="H322" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -10140,7 +10134,7 @@
         <v>59</v>
       </c>
       <c r="H323" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -10166,7 +10160,7 @@
         <v>59</v>
       </c>
       <c r="H324" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -10192,7 +10186,7 @@
         <v>59</v>
       </c>
       <c r="H325" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -10218,7 +10212,7 @@
         <v>59</v>
       </c>
       <c r="H326" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -10244,7 +10238,7 @@
         <v>59</v>
       </c>
       <c r="H327" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -10270,7 +10264,7 @@
         <v>59</v>
       </c>
       <c r="H328" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -10400,7 +10394,7 @@
         <v>59</v>
       </c>
       <c r="H333" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -10478,7 +10472,7 @@
         <v>59</v>
       </c>
       <c r="H336" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -10504,7 +10498,7 @@
         <v>59</v>
       </c>
       <c r="H337" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -10530,7 +10524,7 @@
         <v>67</v>
       </c>
       <c r="H338" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -10634,7 +10628,7 @@
         <v>59</v>
       </c>
       <c r="H342" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -10660,7 +10654,7 @@
         <v>59</v>
       </c>
       <c r="H343" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -10686,7 +10680,7 @@
         <v>59</v>
       </c>
       <c r="H344" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -10712,7 +10706,7 @@
         <v>59</v>
       </c>
       <c r="H345" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -10738,7 +10732,7 @@
         <v>59</v>
       </c>
       <c r="H346" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -10764,7 +10758,7 @@
         <v>59</v>
       </c>
       <c r="H347" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -10842,7 +10836,7 @@
         <v>59</v>
       </c>
       <c r="H350" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -10868,7 +10862,7 @@
         <v>59</v>
       </c>
       <c r="H351" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -10894,7 +10888,7 @@
         <v>59</v>
       </c>
       <c r="H352" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -10920,7 +10914,7 @@
         <v>59</v>
       </c>
       <c r="H353" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -10946,7 +10940,7 @@
         <v>59</v>
       </c>
       <c r="H354" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -10972,7 +10966,7 @@
         <v>59</v>
       </c>
       <c r="H355" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -10998,7 +10992,7 @@
         <v>59</v>
       </c>
       <c r="H356" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -11232,7 +11226,7 @@
         <v>59</v>
       </c>
       <c r="H365" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -11258,7 +11252,7 @@
         <v>59</v>
       </c>
       <c r="H366" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -11284,7 +11278,7 @@
         <v>66</v>
       </c>
       <c r="H367" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -11310,7 +11304,7 @@
         <v>59</v>
       </c>
       <c r="H368" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -11362,7 +11356,7 @@
         <v>59</v>
       </c>
       <c r="H370" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -11388,7 +11382,7 @@
         <v>59</v>
       </c>
       <c r="H371" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -11457,7 +11451,7 @@
         <v>29</v>
       </c>
       <c r="E374">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F374" t="s">
         <v>29</v>
@@ -11466,7 +11460,7 @@
         <v>59</v>
       </c>
       <c r="H374" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -11477,13 +11471,13 @@
         <v>7</v>
       </c>
       <c r="C375">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D375" t="s">
         <v>29</v>
       </c>
       <c r="E375">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F375" t="s">
         <v>29</v>
@@ -11492,7 +11486,7 @@
         <v>59</v>
       </c>
       <c r="H375" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -11518,7 +11512,7 @@
         <v>59</v>
       </c>
       <c r="H376" t="s">
-        <v>90</v>
+        <v>261</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -11596,7 +11590,7 @@
         <v>59</v>
       </c>
       <c r="H379" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -11622,7 +11616,7 @@
         <v>59</v>
       </c>
       <c r="H380" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -11726,7 +11720,7 @@
         <v>59</v>
       </c>
       <c r="H384" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -12064,7 +12058,7 @@
         <v>59</v>
       </c>
       <c r="H397" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -12090,7 +12084,7 @@
         <v>59</v>
       </c>
       <c r="H398" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -12116,7 +12110,7 @@
         <v>59</v>
       </c>
       <c r="H399" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -12168,7 +12162,7 @@
         <v>59</v>
       </c>
       <c r="H401" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -12194,7 +12188,7 @@
         <v>59</v>
       </c>
       <c r="H402" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -12272,7 +12266,7 @@
         <v>59</v>
       </c>
       <c r="H405" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -12298,7 +12292,7 @@
         <v>59</v>
       </c>
       <c r="H406" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -12324,7 +12318,7 @@
         <v>59</v>
       </c>
       <c r="H407" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -12350,7 +12344,7 @@
         <v>59</v>
       </c>
       <c r="H408" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -12376,7 +12370,7 @@
         <v>59</v>
       </c>
       <c r="H409" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -12402,7 +12396,7 @@
         <v>59</v>
       </c>
       <c r="H410" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -12428,7 +12422,7 @@
         <v>59</v>
       </c>
       <c r="H411" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -12454,7 +12448,7 @@
         <v>59</v>
       </c>
       <c r="H412" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -12532,7 +12526,7 @@
         <v>66</v>
       </c>
       <c r="H415" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -12558,7 +12552,7 @@
         <v>59</v>
       </c>
       <c r="H416" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -12662,7 +12656,7 @@
         <v>59</v>
       </c>
       <c r="H420" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -12688,7 +12682,7 @@
         <v>59</v>
       </c>
       <c r="H421" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -12714,7 +12708,7 @@
         <v>59</v>
       </c>
       <c r="H422" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -12740,7 +12734,7 @@
         <v>59</v>
       </c>
       <c r="H423" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -12766,7 +12760,7 @@
         <v>59</v>
       </c>
       <c r="H424" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -12792,7 +12786,7 @@
         <v>59</v>
       </c>
       <c r="H425" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -12818,7 +12812,7 @@
         <v>59</v>
       </c>
       <c r="H426" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -12844,7 +12838,7 @@
         <v>59</v>
       </c>
       <c r="H427" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -12922,7 +12916,7 @@
         <v>59</v>
       </c>
       <c r="H430" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -12948,7 +12942,7 @@
         <v>59</v>
       </c>
       <c r="H431" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -13000,7 +12994,7 @@
         <v>59</v>
       </c>
       <c r="H433" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -13052,7 +13046,7 @@
         <v>59</v>
       </c>
       <c r="H435" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -13078,7 +13072,7 @@
         <v>59</v>
       </c>
       <c r="H436" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -13104,7 +13098,7 @@
         <v>59</v>
       </c>
       <c r="H437" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -13130,7 +13124,7 @@
         <v>59</v>
       </c>
       <c r="H438" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -13156,7 +13150,7 @@
         <v>59</v>
       </c>
       <c r="H439" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -13182,7 +13176,7 @@
         <v>59</v>
       </c>
       <c r="H440" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -13208,7 +13202,7 @@
         <v>59</v>
       </c>
       <c r="H441" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -13225,7 +13219,7 @@
         <v>36</v>
       </c>
       <c r="E442">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F442" t="s">
         <v>36</v>
@@ -13234,7 +13228,7 @@
         <v>59</v>
       </c>
       <c r="H442" t="s">
-        <v>299</v>
+        <v>180</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -13260,7 +13254,7 @@
         <v>59</v>
       </c>
       <c r="H443" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -13277,7 +13271,7 @@
         <v>36</v>
       </c>
       <c r="E444">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F444" t="s">
         <v>36</v>
@@ -13286,7 +13280,7 @@
         <v>59</v>
       </c>
       <c r="H444" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -13303,7 +13297,7 @@
         <v>36</v>
       </c>
       <c r="E445">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F445" t="s">
         <v>36</v>
@@ -13312,7 +13306,7 @@
         <v>59</v>
       </c>
       <c r="H445" t="s">
-        <v>300</v>
+        <v>90</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -13338,7 +13332,7 @@
         <v>59</v>
       </c>
       <c r="H446" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -13494,7 +13488,7 @@
         <v>59</v>
       </c>
       <c r="H452" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -13520,7 +13514,7 @@
         <v>59</v>
       </c>
       <c r="H453" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -13546,7 +13540,7 @@
         <v>59</v>
       </c>
       <c r="H454" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -13572,7 +13566,7 @@
         <v>59</v>
       </c>
       <c r="H455" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -13598,7 +13592,7 @@
         <v>59</v>
       </c>
       <c r="H456" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -13650,7 +13644,7 @@
         <v>59</v>
       </c>
       <c r="H458" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -13676,7 +13670,7 @@
         <v>59</v>
       </c>
       <c r="H459" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -13728,7 +13722,7 @@
         <v>59</v>
       </c>
       <c r="H461" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -13754,7 +13748,7 @@
         <v>59</v>
       </c>
       <c r="H462" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -13780,7 +13774,7 @@
         <v>59</v>
       </c>
       <c r="H463" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -13832,7 +13826,7 @@
         <v>59</v>
       </c>
       <c r="H465" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -13858,7 +13852,7 @@
         <v>59</v>
       </c>
       <c r="H466" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -13884,7 +13878,7 @@
         <v>59</v>
       </c>
       <c r="H467" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -13910,7 +13904,7 @@
         <v>59</v>
       </c>
       <c r="H468" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -13936,7 +13930,7 @@
         <v>59</v>
       </c>
       <c r="H469" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -13962,7 +13956,7 @@
         <v>59</v>
       </c>
       <c r="H470" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -13988,7 +13982,7 @@
         <v>59</v>
       </c>
       <c r="H471" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -14014,7 +14008,7 @@
         <v>59</v>
       </c>
       <c r="H472" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -14040,7 +14034,7 @@
         <v>59</v>
       </c>
       <c r="H473" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -14066,7 +14060,7 @@
         <v>59</v>
       </c>
       <c r="H474" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -14092,7 +14086,7 @@
         <v>59</v>
       </c>
       <c r="H475" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -14118,7 +14112,7 @@
         <v>59</v>
       </c>
       <c r="H476" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -14144,7 +14138,7 @@
         <v>59</v>
       </c>
       <c r="H477" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -14170,7 +14164,7 @@
         <v>59</v>
       </c>
       <c r="H478" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="479" spans="1:8">
@@ -14196,7 +14190,7 @@
         <v>59</v>
       </c>
       <c r="H479" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="480" spans="1:8">
@@ -14222,7 +14216,7 @@
         <v>59</v>
       </c>
       <c r="H480" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -14248,7 +14242,7 @@
         <v>59</v>
       </c>
       <c r="H481" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -14274,7 +14268,7 @@
         <v>59</v>
       </c>
       <c r="H482" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -14300,7 +14294,7 @@
         <v>59</v>
       </c>
       <c r="H483" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -14326,7 +14320,7 @@
         <v>59</v>
       </c>
       <c r="H484" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -14352,7 +14346,7 @@
         <v>59</v>
       </c>
       <c r="H485" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -14369,7 +14363,7 @@
         <v>36</v>
       </c>
       <c r="E486">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F486" t="s">
         <v>36</v>
@@ -14378,7 +14372,7 @@
         <v>59</v>
       </c>
       <c r="H486" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -14404,7 +14398,7 @@
         <v>59</v>
       </c>
       <c r="H487" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="488" spans="1:8">
@@ -14430,7 +14424,7 @@
         <v>59</v>
       </c>
       <c r="H488" t="s">
-        <v>185</v>
+        <v>331</v>
       </c>
     </row>
     <row r="489" spans="1:8">
@@ -14456,7 +14450,7 @@
         <v>59</v>
       </c>
       <c r="H489" t="s">
-        <v>334</v>
+        <v>185</v>
       </c>
     </row>
     <row r="490" spans="1:8">
@@ -14534,7 +14528,7 @@
         <v>59</v>
       </c>
       <c r="H492" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="493" spans="1:8">
@@ -14664,7 +14658,7 @@
         <v>59</v>
       </c>
       <c r="H497" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="498" spans="1:8">
@@ -14716,7 +14710,7 @@
         <v>59</v>
       </c>
       <c r="H499" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="500" spans="1:8">
@@ -14742,7 +14736,7 @@
         <v>59</v>
       </c>
       <c r="H500" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="501" spans="1:8">
@@ -14768,7 +14762,7 @@
         <v>59</v>
       </c>
       <c r="H501" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="502" spans="1:8">
@@ -14794,7 +14788,7 @@
         <v>59</v>
       </c>
       <c r="H502" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="503" spans="1:8">
@@ -14846,7 +14840,7 @@
         <v>59</v>
       </c>
       <c r="H504" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="505" spans="1:8">
@@ -14872,7 +14866,7 @@
         <v>59</v>
       </c>
       <c r="H505" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="506" spans="1:8">
@@ -14898,7 +14892,7 @@
         <v>59</v>
       </c>
       <c r="H506" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="507" spans="1:8">
@@ -14924,7 +14918,7 @@
         <v>59</v>
       </c>
       <c r="H507" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="508" spans="1:8">
@@ -14950,7 +14944,7 @@
         <v>59</v>
       </c>
       <c r="H508" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="509" spans="1:8">
@@ -15080,7 +15074,7 @@
         <v>59</v>
       </c>
       <c r="H513" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="514" spans="1:8">
@@ -15106,7 +15100,7 @@
         <v>59</v>
       </c>
       <c r="H514" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="515" spans="1:8">
@@ -15288,7 +15282,7 @@
         <v>59</v>
       </c>
       <c r="H521" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="522" spans="1:8">
@@ -15314,7 +15308,7 @@
         <v>59</v>
       </c>
       <c r="H522" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -15340,7 +15334,7 @@
         <v>59</v>
       </c>
       <c r="H523" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="524" spans="1:8">
@@ -15392,7 +15386,7 @@
         <v>59</v>
       </c>
       <c r="H525" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -15418,7 +15412,7 @@
         <v>59</v>
       </c>
       <c r="H526" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -15470,7 +15464,7 @@
         <v>59</v>
       </c>
       <c r="H528" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -15496,7 +15490,7 @@
         <v>59</v>
       </c>
       <c r="H529" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -15522,7 +15516,7 @@
         <v>59</v>
       </c>
       <c r="H530" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -15548,7 +15542,7 @@
         <v>59</v>
       </c>
       <c r="H531" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -15574,7 +15568,7 @@
         <v>59</v>
       </c>
       <c r="H532" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -15600,7 +15594,7 @@
         <v>59</v>
       </c>
       <c r="H533" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -15626,7 +15620,7 @@
         <v>59</v>
       </c>
       <c r="H534" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -15652,7 +15646,7 @@
         <v>59</v>
       </c>
       <c r="H535" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -15678,7 +15672,7 @@
         <v>59</v>
       </c>
       <c r="H536" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -15704,7 +15698,7 @@
         <v>59</v>
       </c>
       <c r="H537" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -15730,7 +15724,7 @@
         <v>59</v>
       </c>
       <c r="H538" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="539" spans="1:8">
@@ -15756,7 +15750,7 @@
         <v>59</v>
       </c>
       <c r="H539" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -15782,7 +15776,7 @@
         <v>59</v>
       </c>
       <c r="H540" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -15808,7 +15802,7 @@
         <v>59</v>
       </c>
       <c r="H541" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -15834,7 +15828,7 @@
         <v>59</v>
       </c>
       <c r="H542" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -15860,7 +15854,7 @@
         <v>59</v>
       </c>
       <c r="H543" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -15886,7 +15880,7 @@
         <v>59</v>
       </c>
       <c r="H544" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -15912,7 +15906,7 @@
         <v>59</v>
       </c>
       <c r="H545" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="546" spans="1:8">
@@ -15938,7 +15932,7 @@
         <v>59</v>
       </c>
       <c r="H546" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -15964,7 +15958,7 @@
         <v>59</v>
       </c>
       <c r="H547" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -15990,7 +15984,7 @@
         <v>59</v>
       </c>
       <c r="H548" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="549" spans="1:8">
@@ -16016,7 +16010,7 @@
         <v>59</v>
       </c>
       <c r="H549" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="550" spans="1:8">
@@ -16042,7 +16036,7 @@
         <v>59</v>
       </c>
       <c r="H550" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="551" spans="1:8">
@@ -16068,7 +16062,7 @@
         <v>59</v>
       </c>
       <c r="H551" t="s">
-        <v>188</v>
+        <v>370</v>
       </c>
     </row>
     <row r="552" spans="1:8">
@@ -16094,7 +16088,7 @@
         <v>59</v>
       </c>
       <c r="H552" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="553" spans="1:8">
@@ -16120,7 +16114,7 @@
         <v>59</v>
       </c>
       <c r="H553" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="554" spans="1:8">
@@ -16146,7 +16140,7 @@
         <v>59</v>
       </c>
       <c r="H554" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -16172,7 +16166,7 @@
         <v>59</v>
       </c>
       <c r="H555" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="556" spans="1:8">
@@ -16198,7 +16192,7 @@
         <v>59</v>
       </c>
       <c r="H556" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="557" spans="1:8">
@@ -16224,7 +16218,7 @@
         <v>59</v>
       </c>
       <c r="H557" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="558" spans="1:8">
@@ -16276,7 +16270,7 @@
         <v>59</v>
       </c>
       <c r="H559" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -16484,7 +16478,7 @@
         <v>59</v>
       </c>
       <c r="H567" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="568" spans="1:8">
@@ -16562,7 +16556,7 @@
         <v>59</v>
       </c>
       <c r="H570" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -16588,7 +16582,7 @@
         <v>59</v>
       </c>
       <c r="H571" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="572" spans="1:8">
@@ -16614,7 +16608,7 @@
         <v>59</v>
       </c>
       <c r="H572" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="573" spans="1:8">
@@ -16640,7 +16634,7 @@
         <v>59</v>
       </c>
       <c r="H573" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -16718,7 +16712,7 @@
         <v>59</v>
       </c>
       <c r="H576" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="577" spans="1:8">
@@ -16770,7 +16764,7 @@
         <v>59</v>
       </c>
       <c r="H578" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -16822,7 +16816,7 @@
         <v>59</v>
       </c>
       <c r="H580" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="581" spans="1:8">
@@ -16848,7 +16842,7 @@
         <v>59</v>
       </c>
       <c r="H581" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="582" spans="1:8">
@@ -16900,7 +16894,7 @@
         <v>59</v>
       </c>
       <c r="H583" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -16926,7 +16920,7 @@
         <v>59</v>
       </c>
       <c r="H584" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -16952,7 +16946,7 @@
         <v>59</v>
       </c>
       <c r="H585" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -16978,7 +16972,7 @@
         <v>59</v>
       </c>
       <c r="H586" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -17030,7 +17024,7 @@
         <v>59</v>
       </c>
       <c r="H588" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -17056,7 +17050,7 @@
         <v>59</v>
       </c>
       <c r="H589" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -17082,7 +17076,7 @@
         <v>59</v>
       </c>
       <c r="H590" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="591" spans="1:8">
@@ -17108,7 +17102,7 @@
         <v>59</v>
       </c>
       <c r="H591" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -17134,7 +17128,7 @@
         <v>59</v>
       </c>
       <c r="H592" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -17160,7 +17154,7 @@
         <v>59</v>
       </c>
       <c r="H593" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="594" spans="1:8">
@@ -17186,7 +17180,7 @@
         <v>59</v>
       </c>
       <c r="H594" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="595" spans="1:8">
@@ -17212,7 +17206,7 @@
         <v>59</v>
       </c>
       <c r="H595" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="596" spans="1:8">
@@ -17238,7 +17232,7 @@
         <v>68</v>
       </c>
       <c r="H596" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="597" spans="1:8">
@@ -17264,7 +17258,7 @@
         <v>59</v>
       </c>
       <c r="H597" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="598" spans="1:8">
@@ -17290,7 +17284,7 @@
         <v>59</v>
       </c>
       <c r="H598" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="599" spans="1:8">
@@ -17316,7 +17310,7 @@
         <v>59</v>
       </c>
       <c r="H599" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="600" spans="1:8">
@@ -17342,7 +17336,7 @@
         <v>59</v>
       </c>
       <c r="H600" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="601" spans="1:8">
@@ -17368,7 +17362,7 @@
         <v>59</v>
       </c>
       <c r="H601" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="602" spans="1:8">
@@ -17411,16 +17405,16 @@
         <v>18</v>
       </c>
       <c r="E603">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="F603" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="G603" t="s">
         <v>59</v>
       </c>
       <c r="H603" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="604" spans="1:8">
@@ -17446,7 +17440,7 @@
         <v>59</v>
       </c>
       <c r="H604" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="605" spans="1:8">
@@ -17472,7 +17466,7 @@
         <v>59</v>
       </c>
       <c r="H605" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="606" spans="1:8">
@@ -17498,7 +17492,7 @@
         <v>59</v>
       </c>
       <c r="H606" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="607" spans="1:8">
@@ -17524,7 +17518,7 @@
         <v>59</v>
       </c>
       <c r="H607" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="608" spans="1:8">
@@ -17550,7 +17544,7 @@
         <v>59</v>
       </c>
       <c r="H608" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="609" spans="1:8">
@@ -17576,7 +17570,7 @@
         <v>59</v>
       </c>
       <c r="H609" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="610" spans="1:8">
@@ -17602,7 +17596,7 @@
         <v>59</v>
       </c>
       <c r="H610" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -17654,7 +17648,7 @@
         <v>59</v>
       </c>
       <c r="H612" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -17680,7 +17674,7 @@
         <v>59</v>
       </c>
       <c r="H613" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="614" spans="1:8">
@@ -17758,7 +17752,7 @@
         <v>59</v>
       </c>
       <c r="H616" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -17784,7 +17778,7 @@
         <v>59</v>
       </c>
       <c r="H617" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="618" spans="1:8">
@@ -17810,7 +17804,7 @@
         <v>59</v>
       </c>
       <c r="H618" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -17940,7 +17934,7 @@
         <v>59</v>
       </c>
       <c r="H623" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -17992,7 +17986,7 @@
         <v>59</v>
       </c>
       <c r="H625" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="626" spans="1:8">
@@ -18018,7 +18012,7 @@
         <v>59</v>
       </c>
       <c r="H626" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="627" spans="1:8">
@@ -18044,7 +18038,7 @@
         <v>59</v>
       </c>
       <c r="H627" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="628" spans="1:8">
@@ -18070,7 +18064,7 @@
         <v>59</v>
       </c>
       <c r="H628" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="629" spans="1:8">
@@ -18122,7 +18116,7 @@
         <v>59</v>
       </c>
       <c r="H630" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="631" spans="1:8">
@@ -18148,7 +18142,7 @@
         <v>59</v>
       </c>
       <c r="H631" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="632" spans="1:8">
@@ -18200,7 +18194,7 @@
         <v>59</v>
       </c>
       <c r="H633" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -18226,7 +18220,7 @@
         <v>59</v>
       </c>
       <c r="H634" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -18252,7 +18246,7 @@
         <v>59</v>
       </c>
       <c r="H635" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="636" spans="1:8">
@@ -18278,7 +18272,7 @@
         <v>59</v>
       </c>
       <c r="H636" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="637" spans="1:8">
@@ -18304,7 +18298,7 @@
         <v>59</v>
       </c>
       <c r="H637" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="638" spans="1:8">
@@ -18330,7 +18324,7 @@
         <v>59</v>
       </c>
       <c r="H638" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="639" spans="1:8">
@@ -18382,7 +18376,7 @@
         <v>59</v>
       </c>
       <c r="H640" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="641" spans="1:8">
@@ -18408,7 +18402,7 @@
         <v>59</v>
       </c>
       <c r="H641" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="642" spans="1:8">
@@ -18486,7 +18480,7 @@
         <v>59</v>
       </c>
       <c r="H644" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="645" spans="1:8">
@@ -18512,7 +18506,7 @@
         <v>59</v>
       </c>
       <c r="H645" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="646" spans="1:8">
@@ -18538,7 +18532,7 @@
         <v>59</v>
       </c>
       <c r="H646" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="647" spans="1:8">
@@ -18616,7 +18610,7 @@
         <v>59</v>
       </c>
       <c r="H649" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="650" spans="1:8">
@@ -18642,7 +18636,7 @@
         <v>59</v>
       </c>
       <c r="H650" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="651" spans="1:8">
@@ -18668,7 +18662,7 @@
         <v>59</v>
       </c>
       <c r="H651" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="652" spans="1:8">
@@ -18694,7 +18688,7 @@
         <v>59</v>
       </c>
       <c r="H652" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -18746,7 +18740,7 @@
         <v>59</v>
       </c>
       <c r="H654" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="655" spans="1:8">
@@ -18772,7 +18766,7 @@
         <v>59</v>
       </c>
       <c r="H655" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="656" spans="1:8">
@@ -18824,7 +18818,7 @@
         <v>59</v>
       </c>
       <c r="H657" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="658" spans="1:8">
@@ -18850,7 +18844,7 @@
         <v>59</v>
       </c>
       <c r="H658" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -18876,7 +18870,7 @@
         <v>59</v>
       </c>
       <c r="H659" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="660" spans="1:8">
@@ -18902,7 +18896,7 @@
         <v>59</v>
       </c>
       <c r="H660" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="661" spans="1:8">
@@ -18928,7 +18922,7 @@
         <v>59</v>
       </c>
       <c r="H661" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="662" spans="1:8">
@@ -18954,7 +18948,7 @@
         <v>59</v>
       </c>
       <c r="H662" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="663" spans="1:8">
@@ -18980,7 +18974,7 @@
         <v>59</v>
       </c>
       <c r="H663" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="664" spans="1:8">
@@ -19006,7 +19000,7 @@
         <v>59</v>
       </c>
       <c r="H664" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -19032,7 +19026,7 @@
         <v>59</v>
       </c>
       <c r="H665" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="666" spans="1:8">
@@ -19058,7 +19052,7 @@
         <v>59</v>
       </c>
       <c r="H666" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="667" spans="1:8">
@@ -19084,7 +19078,7 @@
         <v>59</v>
       </c>
       <c r="H667" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="668" spans="1:8">
@@ -19110,7 +19104,7 @@
         <v>59</v>
       </c>
       <c r="H668" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="669" spans="1:8">
@@ -19136,7 +19130,7 @@
         <v>59</v>
       </c>
       <c r="H669" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="670" spans="1:8">
@@ -19162,7 +19156,7 @@
         <v>59</v>
       </c>
       <c r="H670" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="671" spans="1:8">
@@ -19188,7 +19182,7 @@
         <v>59</v>
       </c>
       <c r="H671" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="672" spans="1:8">
@@ -19214,7 +19208,7 @@
         <v>59</v>
       </c>
       <c r="H672" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="673" spans="1:8">
@@ -19240,7 +19234,7 @@
         <v>59</v>
       </c>
       <c r="H673" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="674" spans="1:8">
@@ -19266,7 +19260,7 @@
         <v>59</v>
       </c>
       <c r="H674" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="675" spans="1:8">
@@ -19292,7 +19286,7 @@
         <v>59</v>
       </c>
       <c r="H675" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="676" spans="1:8">
@@ -19318,7 +19312,7 @@
         <v>59</v>
       </c>
       <c r="H676" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="677" spans="1:8">
@@ -19344,7 +19338,7 @@
         <v>59</v>
       </c>
       <c r="H677" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="678" spans="1:8">
@@ -19370,7 +19364,7 @@
         <v>59</v>
       </c>
       <c r="H678" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="679" spans="1:8">
@@ -19396,7 +19390,7 @@
         <v>59</v>
       </c>
       <c r="H679" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="680" spans="1:8">
@@ -19448,7 +19442,7 @@
         <v>59</v>
       </c>
       <c r="H681" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="682" spans="1:8">
@@ -19474,7 +19468,7 @@
         <v>59</v>
       </c>
       <c r="H682" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="683" spans="1:8">
@@ -19500,7 +19494,7 @@
         <v>59</v>
       </c>
       <c r="H683" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="684" spans="1:8">
@@ -19526,7 +19520,7 @@
         <v>59</v>
       </c>
       <c r="H684" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="685" spans="1:8">
@@ -19552,7 +19546,7 @@
         <v>59</v>
       </c>
       <c r="H685" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="686" spans="1:8">
@@ -19578,7 +19572,7 @@
         <v>59</v>
       </c>
       <c r="H686" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="687" spans="1:8">
@@ -19604,7 +19598,7 @@
         <v>59</v>
       </c>
       <c r="H687" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_raj/Backend/Backend/Tagging_Sheet_Pre.xlsx
+++ b/pds_admin_raj/Backend/Backend/Tagging_Sheet_Pre.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3462" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3462" uniqueCount="457">
   <si>
     <t>Var</t>
   </si>
@@ -559,10 +559,10 @@
     <t>64400.0</t>
   </si>
   <si>
-    <t>71400.0</t>
-  </si>
-  <si>
-    <t>117160.0</t>
+    <t>9060.0</t>
+  </si>
+  <si>
+    <t>179500.0</t>
   </si>
   <si>
     <t>57960.0</t>
@@ -580,24 +580,24 @@
     <t>17520.0</t>
   </si>
   <si>
-    <t>22540.0</t>
+    <t>15540.0</t>
+  </si>
+  <si>
+    <t>67200.0</t>
+  </si>
+  <si>
+    <t>30070.0</t>
+  </si>
+  <si>
+    <t>18298.0</t>
+  </si>
+  <si>
+    <t>22200.0</t>
   </si>
   <si>
     <t>60200.0</t>
   </si>
   <si>
-    <t>30070.0</t>
-  </si>
-  <si>
-    <t>18298.0</t>
-  </si>
-  <si>
-    <t>15200.0</t>
-  </si>
-  <si>
-    <t>67200.0</t>
-  </si>
-  <si>
     <t>38120.0</t>
   </si>
   <si>
@@ -631,10 +631,13 @@
     <t>44800.0</t>
   </si>
   <si>
+    <t>42647.5</t>
+  </si>
+  <si>
     <t>128070.0</t>
   </si>
   <si>
-    <t>85460.0</t>
+    <t>87612.5</t>
   </si>
   <si>
     <t>2152.5</t>
@@ -793,13 +796,10 @@
     <t>6429.07</t>
   </si>
   <si>
-    <t>28520.0</t>
-  </si>
-  <si>
     <t>17390.2</t>
   </si>
   <si>
-    <t>9999.8</t>
+    <t>11129.8</t>
   </si>
   <si>
     <t>8459.0</t>
@@ -904,241 +904,244 @@
     <t>42830.0</t>
   </si>
   <si>
+    <t>9010.0</t>
+  </si>
+  <si>
     <t>36400.0</t>
   </si>
   <si>
+    <t>35790.0</t>
+  </si>
+  <si>
+    <t>102420.0</t>
+  </si>
+  <si>
+    <t>10300.0</t>
+  </si>
+  <si>
+    <t>660.0</t>
+  </si>
+  <si>
+    <t>40400.0</t>
+  </si>
+  <si>
+    <t>58800.0</t>
+  </si>
+  <si>
+    <t>51600.0</t>
+  </si>
+  <si>
+    <t>44500.0</t>
+  </si>
+  <si>
+    <t>138110.0</t>
+  </si>
+  <si>
+    <t>18589.0</t>
+  </si>
+  <si>
+    <t>32430.0</t>
+  </si>
+  <si>
+    <t>40281.0</t>
+  </si>
+  <si>
+    <t>54339.86</t>
+  </si>
+  <si>
+    <t>3040.0</t>
+  </si>
+  <si>
+    <t>33700.0</t>
+  </si>
+  <si>
+    <t>74870.0</t>
+  </si>
+  <si>
+    <t>84450.0</t>
+  </si>
+  <si>
+    <t>54139.0</t>
+  </si>
+  <si>
+    <t>9771.0</t>
+  </si>
+  <si>
+    <t>5140.0</t>
+  </si>
+  <si>
+    <t>61600.0</t>
+  </si>
+  <si>
+    <t>74700.0</t>
+  </si>
+  <si>
+    <t>144014.5</t>
+  </si>
+  <si>
+    <t>51285.5</t>
+  </si>
+  <si>
+    <t>88500.0</t>
+  </si>
+  <si>
+    <t>33684.5</t>
+  </si>
+  <si>
+    <t>81500.0</t>
+  </si>
+  <si>
+    <t>40300.0</t>
+  </si>
+  <si>
+    <t>66560.0</t>
+  </si>
+  <si>
+    <t>58700.0</t>
+  </si>
+  <si>
+    <t>69200.0</t>
+  </si>
+  <si>
+    <t>30680.0</t>
+  </si>
+  <si>
+    <t>34500.0</t>
+  </si>
+  <si>
+    <t>2920.0</t>
+  </si>
+  <si>
+    <t>21780.0</t>
+  </si>
+  <si>
+    <t>21480.0</t>
+  </si>
+  <si>
+    <t>20249.28</t>
+  </si>
+  <si>
+    <t>24722.86</t>
+  </si>
+  <si>
+    <t>13420.0</t>
+  </si>
+  <si>
+    <t>4840.0</t>
+  </si>
+  <si>
+    <t>11701.0</t>
+  </si>
+  <si>
+    <t>6559.0</t>
+  </si>
+  <si>
+    <t>25277.14</t>
+  </si>
+  <si>
+    <t>2112.86</t>
+  </si>
+  <si>
+    <t>6833.26</t>
+  </si>
+  <si>
+    <t>16207.36</t>
+  </si>
+  <si>
+    <t>11182.64</t>
+  </si>
+  <si>
+    <t>97450.0</t>
+  </si>
+  <si>
+    <t>8890.0</t>
+  </si>
+  <si>
+    <t>18500.0</t>
+  </si>
+  <si>
+    <t>18000.0</t>
+  </si>
+  <si>
+    <t>18637.0</t>
+  </si>
+  <si>
+    <t>30550.0</t>
+  </si>
+  <si>
+    <t>11570.0</t>
+  </si>
+  <si>
+    <t>36270.0</t>
+  </si>
+  <si>
+    <t>40000.0</t>
+  </si>
+  <si>
+    <t>30250.0</t>
+  </si>
+  <si>
+    <t>17340.0</t>
+  </si>
+  <si>
+    <t>14380.0</t>
+  </si>
+  <si>
+    <t>30000.0</t>
+  </si>
+  <si>
+    <t>48000.0</t>
+  </si>
+  <si>
+    <t>71389.14</t>
+  </si>
+  <si>
+    <t>69270.0</t>
+  </si>
+  <si>
+    <t>10720.86</t>
+  </si>
+  <si>
+    <t>50000.0</t>
+  </si>
+  <si>
+    <t>20880.0</t>
+  </si>
+  <si>
+    <t>31320.0</t>
+  </si>
+  <si>
+    <t>26278.36</t>
+  </si>
+  <si>
+    <t>27000.0</t>
+  </si>
+  <si>
+    <t>30190.0</t>
+  </si>
+  <si>
+    <t>113731.64</t>
+  </si>
+  <si>
+    <t>11810.0</t>
+  </si>
+  <si>
+    <t>37740.0</t>
+  </si>
+  <si>
+    <t>30980.0</t>
+  </si>
+  <si>
+    <t>34352.0</t>
+  </si>
+  <si>
+    <t>57400.0</t>
+  </si>
+  <si>
+    <t>17430.0</t>
+  </si>
+  <si>
     <t>37010.0</t>
-  </si>
-  <si>
-    <t>102420.0</t>
-  </si>
-  <si>
-    <t>10300.0</t>
-  </si>
-  <si>
-    <t>660.0</t>
-  </si>
-  <si>
-    <t>40400.0</t>
-  </si>
-  <si>
-    <t>58800.0</t>
-  </si>
-  <si>
-    <t>51600.0</t>
-  </si>
-  <si>
-    <t>44500.0</t>
-  </si>
-  <si>
-    <t>138110.0</t>
-  </si>
-  <si>
-    <t>18589.0</t>
-  </si>
-  <si>
-    <t>32430.0</t>
-  </si>
-  <si>
-    <t>40281.0</t>
-  </si>
-  <si>
-    <t>54339.86</t>
-  </si>
-  <si>
-    <t>3040.0</t>
-  </si>
-  <si>
-    <t>33700.0</t>
-  </si>
-  <si>
-    <t>74870.0</t>
-  </si>
-  <si>
-    <t>84450.0</t>
-  </si>
-  <si>
-    <t>54139.0</t>
-  </si>
-  <si>
-    <t>9771.0</t>
-  </si>
-  <si>
-    <t>71700.0</t>
-  </si>
-  <si>
-    <t>56640.0</t>
-  </si>
-  <si>
-    <t>74700.0</t>
-  </si>
-  <si>
-    <t>144014.5</t>
-  </si>
-  <si>
-    <t>51285.5</t>
-  </si>
-  <si>
-    <t>88500.0</t>
-  </si>
-  <si>
-    <t>33684.5</t>
-  </si>
-  <si>
-    <t>81500.0</t>
-  </si>
-  <si>
-    <t>40300.0</t>
-  </si>
-  <si>
-    <t>61600.0</t>
-  </si>
-  <si>
-    <t>4960.0</t>
-  </si>
-  <si>
-    <t>58700.0</t>
-  </si>
-  <si>
-    <t>69200.0</t>
-  </si>
-  <si>
-    <t>30680.0</t>
-  </si>
-  <si>
-    <t>34500.0</t>
-  </si>
-  <si>
-    <t>2920.0</t>
-  </si>
-  <si>
-    <t>21780.0</t>
-  </si>
-  <si>
-    <t>21480.0</t>
-  </si>
-  <si>
-    <t>20249.28</t>
-  </si>
-  <si>
-    <t>24722.86</t>
-  </si>
-  <si>
-    <t>13420.0</t>
-  </si>
-  <si>
-    <t>4840.0</t>
-  </si>
-  <si>
-    <t>11701.0</t>
-  </si>
-  <si>
-    <t>6559.0</t>
-  </si>
-  <si>
-    <t>25277.14</t>
-  </si>
-  <si>
-    <t>2112.86</t>
-  </si>
-  <si>
-    <t>6833.26</t>
-  </si>
-  <si>
-    <t>16207.36</t>
-  </si>
-  <si>
-    <t>11182.64</t>
-  </si>
-  <si>
-    <t>97450.0</t>
-  </si>
-  <si>
-    <t>8890.0</t>
-  </si>
-  <si>
-    <t>18500.0</t>
-  </si>
-  <si>
-    <t>18000.0</t>
-  </si>
-  <si>
-    <t>18637.0</t>
-  </si>
-  <si>
-    <t>30550.0</t>
-  </si>
-  <si>
-    <t>11570.0</t>
-  </si>
-  <si>
-    <t>36270.0</t>
-  </si>
-  <si>
-    <t>40000.0</t>
-  </si>
-  <si>
-    <t>30250.0</t>
-  </si>
-  <si>
-    <t>17340.0</t>
-  </si>
-  <si>
-    <t>14380.0</t>
-  </si>
-  <si>
-    <t>30000.0</t>
-  </si>
-  <si>
-    <t>48000.0</t>
-  </si>
-  <si>
-    <t>71389.14</t>
-  </si>
-  <si>
-    <t>69270.0</t>
-  </si>
-  <si>
-    <t>10720.86</t>
-  </si>
-  <si>
-    <t>50000.0</t>
-  </si>
-  <si>
-    <t>20880.0</t>
-  </si>
-  <si>
-    <t>31320.0</t>
-  </si>
-  <si>
-    <t>26278.36</t>
-  </si>
-  <si>
-    <t>27000.0</t>
-  </si>
-  <si>
-    <t>30190.0</t>
-  </si>
-  <si>
-    <t>113731.64</t>
-  </si>
-  <si>
-    <t>11810.0</t>
-  </si>
-  <si>
-    <t>37740.0</t>
-  </si>
-  <si>
-    <t>30980.0</t>
-  </si>
-  <si>
-    <t>34352.0</t>
-  </si>
-  <si>
-    <t>57400.0</t>
-  </si>
-  <si>
-    <t>17430.0</t>
   </si>
   <si>
     <t>15520.0</t>
@@ -8461,7 +8464,7 @@
         <v>18</v>
       </c>
       <c r="E259">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -8539,7 +8542,7 @@
         <v>18</v>
       </c>
       <c r="E262">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -8643,7 +8646,7 @@
         <v>18</v>
       </c>
       <c r="E266">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -8704,7 +8707,7 @@
         <v>59</v>
       </c>
       <c r="H268" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -9068,7 +9071,7 @@
         <v>59</v>
       </c>
       <c r="H282" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -9094,7 +9097,7 @@
         <v>59</v>
       </c>
       <c r="H283" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9120,7 +9123,7 @@
         <v>59</v>
       </c>
       <c r="H284" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -9137,7 +9140,7 @@
         <v>18</v>
       </c>
       <c r="E285">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="F285" t="s">
         <v>18</v>
@@ -9146,7 +9149,7 @@
         <v>59</v>
       </c>
       <c r="H285" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -9198,7 +9201,7 @@
         <v>59</v>
       </c>
       <c r="H287" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -9224,7 +9227,7 @@
         <v>59</v>
       </c>
       <c r="H288" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -9250,7 +9253,7 @@
         <v>59</v>
       </c>
       <c r="H289" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -9276,7 +9279,7 @@
         <v>59</v>
       </c>
       <c r="H290" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -9302,7 +9305,7 @@
         <v>59</v>
       </c>
       <c r="H291" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -9328,7 +9331,7 @@
         <v>59</v>
       </c>
       <c r="H292" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -9354,7 +9357,7 @@
         <v>59</v>
       </c>
       <c r="H293" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -9380,7 +9383,7 @@
         <v>59</v>
       </c>
       <c r="H294" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -9406,7 +9409,7 @@
         <v>59</v>
       </c>
       <c r="H295" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -9458,7 +9461,7 @@
         <v>59</v>
       </c>
       <c r="H297" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -9484,7 +9487,7 @@
         <v>59</v>
       </c>
       <c r="H298" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -9510,7 +9513,7 @@
         <v>59</v>
       </c>
       <c r="H299" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -9536,7 +9539,7 @@
         <v>59</v>
       </c>
       <c r="H300" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -9562,7 +9565,7 @@
         <v>59</v>
       </c>
       <c r="H301" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -9614,7 +9617,7 @@
         <v>59</v>
       </c>
       <c r="H303" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -9640,7 +9643,7 @@
         <v>59</v>
       </c>
       <c r="H304" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -9666,7 +9669,7 @@
         <v>59</v>
       </c>
       <c r="H305" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -9692,7 +9695,7 @@
         <v>59</v>
       </c>
       <c r="H306" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -9718,7 +9721,7 @@
         <v>59</v>
       </c>
       <c r="H307" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -9770,7 +9773,7 @@
         <v>59</v>
       </c>
       <c r="H309" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -9796,7 +9799,7 @@
         <v>59</v>
       </c>
       <c r="H310" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -9848,7 +9851,7 @@
         <v>59</v>
       </c>
       <c r="H312" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -9874,7 +9877,7 @@
         <v>59</v>
       </c>
       <c r="H313" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -9900,7 +9903,7 @@
         <v>59</v>
       </c>
       <c r="H314" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10108,7 +10111,7 @@
         <v>59</v>
       </c>
       <c r="H322" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -10134,7 +10137,7 @@
         <v>59</v>
       </c>
       <c r="H323" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -10160,7 +10163,7 @@
         <v>59</v>
       </c>
       <c r="H324" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -10186,7 +10189,7 @@
         <v>59</v>
       </c>
       <c r="H325" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -10212,7 +10215,7 @@
         <v>59</v>
       </c>
       <c r="H326" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -10238,7 +10241,7 @@
         <v>59</v>
       </c>
       <c r="H327" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -10264,7 +10267,7 @@
         <v>59</v>
       </c>
       <c r="H328" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -10394,7 +10397,7 @@
         <v>59</v>
       </c>
       <c r="H333" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -10472,7 +10475,7 @@
         <v>59</v>
       </c>
       <c r="H336" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -10498,7 +10501,7 @@
         <v>59</v>
       </c>
       <c r="H337" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -10524,7 +10527,7 @@
         <v>67</v>
       </c>
       <c r="H338" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -10628,7 +10631,7 @@
         <v>59</v>
       </c>
       <c r="H342" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -10654,7 +10657,7 @@
         <v>59</v>
       </c>
       <c r="H343" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -10680,7 +10683,7 @@
         <v>59</v>
       </c>
       <c r="H344" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -10706,7 +10709,7 @@
         <v>59</v>
       </c>
       <c r="H345" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -10732,7 +10735,7 @@
         <v>59</v>
       </c>
       <c r="H346" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -10758,7 +10761,7 @@
         <v>59</v>
       </c>
       <c r="H347" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -10836,7 +10839,7 @@
         <v>59</v>
       </c>
       <c r="H350" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -10862,7 +10865,7 @@
         <v>59</v>
       </c>
       <c r="H351" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -10888,7 +10891,7 @@
         <v>59</v>
       </c>
       <c r="H352" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -10914,7 +10917,7 @@
         <v>59</v>
       </c>
       <c r="H353" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -10940,7 +10943,7 @@
         <v>59</v>
       </c>
       <c r="H354" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -10966,7 +10969,7 @@
         <v>59</v>
       </c>
       <c r="H355" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -10992,7 +10995,7 @@
         <v>59</v>
       </c>
       <c r="H356" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -11226,7 +11229,7 @@
         <v>59</v>
       </c>
       <c r="H365" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -11252,7 +11255,7 @@
         <v>59</v>
       </c>
       <c r="H366" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -11278,7 +11281,7 @@
         <v>66</v>
       </c>
       <c r="H367" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -11304,7 +11307,7 @@
         <v>59</v>
       </c>
       <c r="H368" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -11356,7 +11359,7 @@
         <v>59</v>
       </c>
       <c r="H370" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -11382,7 +11385,7 @@
         <v>59</v>
       </c>
       <c r="H371" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -11451,7 +11454,7 @@
         <v>29</v>
       </c>
       <c r="E374">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F374" t="s">
         <v>29</v>
@@ -11460,7 +11463,7 @@
         <v>59</v>
       </c>
       <c r="H374" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -11471,13 +11474,13 @@
         <v>7</v>
       </c>
       <c r="C375">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D375" t="s">
         <v>29</v>
       </c>
       <c r="E375">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F375" t="s">
         <v>29</v>
@@ -11486,7 +11489,7 @@
         <v>59</v>
       </c>
       <c r="H375" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -11512,7 +11515,7 @@
         <v>59</v>
       </c>
       <c r="H376" t="s">
-        <v>261</v>
+        <v>90</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -13193,7 +13196,7 @@
         <v>36</v>
       </c>
       <c r="E441">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F441" t="s">
         <v>36</v>
@@ -13202,7 +13205,7 @@
         <v>59</v>
       </c>
       <c r="H441" t="s">
-        <v>296</v>
+        <v>180</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -13219,7 +13222,7 @@
         <v>36</v>
       </c>
       <c r="E442">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F442" t="s">
         <v>36</v>
@@ -13228,7 +13231,7 @@
         <v>59</v>
       </c>
       <c r="H442" t="s">
-        <v>180</v>
+        <v>296</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -13254,7 +13257,7 @@
         <v>59</v>
       </c>
       <c r="H443" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -13271,7 +13274,7 @@
         <v>36</v>
       </c>
       <c r="E444">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F444" t="s">
         <v>36</v>
@@ -13280,7 +13283,7 @@
         <v>59</v>
       </c>
       <c r="H444" t="s">
-        <v>204</v>
+        <v>297</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -13297,7 +13300,7 @@
         <v>36</v>
       </c>
       <c r="E445">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F445" t="s">
         <v>36</v>
@@ -13306,7 +13309,7 @@
         <v>59</v>
       </c>
       <c r="H445" t="s">
-        <v>90</v>
+        <v>298</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -13332,7 +13335,7 @@
         <v>59</v>
       </c>
       <c r="H446" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -13488,7 +13491,7 @@
         <v>59</v>
       </c>
       <c r="H452" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -13514,7 +13517,7 @@
         <v>59</v>
       </c>
       <c r="H453" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -13540,7 +13543,7 @@
         <v>59</v>
       </c>
       <c r="H454" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -13566,7 +13569,7 @@
         <v>59</v>
       </c>
       <c r="H455" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -13592,7 +13595,7 @@
         <v>59</v>
       </c>
       <c r="H456" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -13644,7 +13647,7 @@
         <v>59</v>
       </c>
       <c r="H458" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -13670,7 +13673,7 @@
         <v>59</v>
       </c>
       <c r="H459" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -13722,7 +13725,7 @@
         <v>59</v>
       </c>
       <c r="H461" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -13748,7 +13751,7 @@
         <v>59</v>
       </c>
       <c r="H462" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -13774,7 +13777,7 @@
         <v>59</v>
       </c>
       <c r="H463" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -13826,7 +13829,7 @@
         <v>59</v>
       </c>
       <c r="H465" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -13852,7 +13855,7 @@
         <v>59</v>
       </c>
       <c r="H466" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -13878,7 +13881,7 @@
         <v>59</v>
       </c>
       <c r="H467" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -13904,7 +13907,7 @@
         <v>59</v>
       </c>
       <c r="H468" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -13956,7 +13959,7 @@
         <v>59</v>
       </c>
       <c r="H470" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -13982,7 +13985,7 @@
         <v>59</v>
       </c>
       <c r="H471" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -14008,7 +14011,7 @@
         <v>59</v>
       </c>
       <c r="H472" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -14034,7 +14037,7 @@
         <v>59</v>
       </c>
       <c r="H473" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -14051,7 +14054,7 @@
         <v>36</v>
       </c>
       <c r="E474">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F474" t="s">
         <v>36</v>
@@ -14060,7 +14063,7 @@
         <v>59</v>
       </c>
       <c r="H474" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -14071,13 +14074,13 @@
         <v>7</v>
       </c>
       <c r="C475">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D475" t="s">
         <v>36</v>
       </c>
       <c r="E475">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F475" t="s">
         <v>36</v>
@@ -14103,7 +14106,7 @@
         <v>36</v>
       </c>
       <c r="E476">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F476" t="s">
         <v>36</v>
@@ -14129,7 +14132,7 @@
         <v>36</v>
       </c>
       <c r="E477">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F477" t="s">
         <v>36</v>
@@ -14149,13 +14152,13 @@
         <v>7</v>
       </c>
       <c r="C478">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D478" t="s">
         <v>36</v>
       </c>
       <c r="E478">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F478" t="s">
         <v>36</v>
@@ -14181,7 +14184,7 @@
         <v>36</v>
       </c>
       <c r="E479">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="F479" t="s">
         <v>36</v>
@@ -14201,13 +14204,13 @@
         <v>7</v>
       </c>
       <c r="C480">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D480" t="s">
         <v>36</v>
       </c>
       <c r="E480">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F480" t="s">
         <v>36</v>
@@ -14233,7 +14236,7 @@
         <v>36</v>
       </c>
       <c r="E481">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F481" t="s">
         <v>36</v>
@@ -14253,13 +14256,13 @@
         <v>7</v>
       </c>
       <c r="C482">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D482" t="s">
         <v>36</v>
       </c>
       <c r="E482">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F482" t="s">
         <v>36</v>
@@ -14285,7 +14288,7 @@
         <v>36</v>
       </c>
       <c r="E483">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F483" t="s">
         <v>36</v>
@@ -14363,7 +14366,7 @@
         <v>36</v>
       </c>
       <c r="E486">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F486" t="s">
         <v>36</v>
@@ -14424,7 +14427,7 @@
         <v>59</v>
       </c>
       <c r="H488" t="s">
-        <v>331</v>
+        <v>185</v>
       </c>
     </row>
     <row r="489" spans="1:8">
@@ -14450,7 +14453,7 @@
         <v>59</v>
       </c>
       <c r="H489" t="s">
-        <v>185</v>
+        <v>331</v>
       </c>
     </row>
     <row r="490" spans="1:8">
@@ -16192,7 +16195,7 @@
         <v>59</v>
       </c>
       <c r="H556" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="557" spans="1:8">
@@ -16270,7 +16273,7 @@
         <v>59</v>
       </c>
       <c r="H559" t="s">
-        <v>297</v>
+        <v>375</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -16478,7 +16481,7 @@
         <v>59</v>
       </c>
       <c r="H567" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="568" spans="1:8">
@@ -16556,7 +16559,7 @@
         <v>59</v>
       </c>
       <c r="H570" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -16582,7 +16585,7 @@
         <v>59</v>
       </c>
       <c r="H571" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="572" spans="1:8">
@@ -16608,7 +16611,7 @@
         <v>59</v>
       </c>
       <c r="H572" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="573" spans="1:8">
@@ -16634,7 +16637,7 @@
         <v>59</v>
       </c>
       <c r="H573" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -16712,7 +16715,7 @@
         <v>59</v>
       </c>
       <c r="H576" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="577" spans="1:8">
@@ -16764,7 +16767,7 @@
         <v>59</v>
       </c>
       <c r="H578" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -16842,7 +16845,7 @@
         <v>59</v>
       </c>
       <c r="H581" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="582" spans="1:8">
@@ -16894,7 +16897,7 @@
         <v>59</v>
       </c>
       <c r="H583" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -16920,7 +16923,7 @@
         <v>59</v>
       </c>
       <c r="H584" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -16946,7 +16949,7 @@
         <v>59</v>
       </c>
       <c r="H585" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -16972,7 +16975,7 @@
         <v>59</v>
       </c>
       <c r="H586" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -17024,7 +17027,7 @@
         <v>59</v>
       </c>
       <c r="H588" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -17050,7 +17053,7 @@
         <v>59</v>
       </c>
       <c r="H589" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -17076,7 +17079,7 @@
         <v>59</v>
       </c>
       <c r="H590" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="591" spans="1:8">
@@ -17102,7 +17105,7 @@
         <v>59</v>
       </c>
       <c r="H591" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -17128,7 +17131,7 @@
         <v>59</v>
       </c>
       <c r="H592" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -17154,7 +17157,7 @@
         <v>59</v>
       </c>
       <c r="H593" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="594" spans="1:8">
@@ -17180,7 +17183,7 @@
         <v>59</v>
       </c>
       <c r="H594" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="595" spans="1:8">
@@ -17206,7 +17209,7 @@
         <v>59</v>
       </c>
       <c r="H595" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="596" spans="1:8">
@@ -17232,7 +17235,7 @@
         <v>68</v>
       </c>
       <c r="H596" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="597" spans="1:8">
@@ -17258,7 +17261,7 @@
         <v>59</v>
       </c>
       <c r="H597" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="598" spans="1:8">
@@ -17284,7 +17287,7 @@
         <v>59</v>
       </c>
       <c r="H598" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="599" spans="1:8">
@@ -17310,7 +17313,7 @@
         <v>59</v>
       </c>
       <c r="H599" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="600" spans="1:8">
@@ -17336,7 +17339,7 @@
         <v>59</v>
       </c>
       <c r="H600" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="601" spans="1:8">
@@ -17362,7 +17365,7 @@
         <v>59</v>
       </c>
       <c r="H601" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="602" spans="1:8">
@@ -17414,7 +17417,7 @@
         <v>59</v>
       </c>
       <c r="H603" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="604" spans="1:8">
@@ -17440,7 +17443,7 @@
         <v>59</v>
       </c>
       <c r="H604" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="605" spans="1:8">
@@ -17466,7 +17469,7 @@
         <v>59</v>
       </c>
       <c r="H605" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="606" spans="1:8">
@@ -17492,7 +17495,7 @@
         <v>59</v>
       </c>
       <c r="H606" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="607" spans="1:8">
@@ -17518,7 +17521,7 @@
         <v>59</v>
       </c>
       <c r="H607" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="608" spans="1:8">
@@ -17544,7 +17547,7 @@
         <v>59</v>
       </c>
       <c r="H608" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="609" spans="1:8">
@@ -17570,7 +17573,7 @@
         <v>59</v>
       </c>
       <c r="H609" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="610" spans="1:8">
@@ -17596,7 +17599,7 @@
         <v>59</v>
       </c>
       <c r="H610" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -17648,7 +17651,7 @@
         <v>59</v>
       </c>
       <c r="H612" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -17674,7 +17677,7 @@
         <v>59</v>
       </c>
       <c r="H613" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="614" spans="1:8">
@@ -17752,7 +17755,7 @@
         <v>59</v>
       </c>
       <c r="H616" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -17778,7 +17781,7 @@
         <v>59</v>
       </c>
       <c r="H617" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="618" spans="1:8">
@@ -17804,7 +17807,7 @@
         <v>59</v>
       </c>
       <c r="H618" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -17934,7 +17937,7 @@
         <v>59</v>
       </c>
       <c r="H623" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -17986,7 +17989,7 @@
         <v>59</v>
       </c>
       <c r="H625" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="626" spans="1:8">
@@ -18012,7 +18015,7 @@
         <v>59</v>
       </c>
       <c r="H626" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="627" spans="1:8">
@@ -18038,7 +18041,7 @@
         <v>59</v>
       </c>
       <c r="H627" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="628" spans="1:8">
@@ -18064,7 +18067,7 @@
         <v>59</v>
       </c>
       <c r="H628" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="629" spans="1:8">
@@ -18116,7 +18119,7 @@
         <v>59</v>
       </c>
       <c r="H630" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="631" spans="1:8">
@@ -18142,7 +18145,7 @@
         <v>59</v>
       </c>
       <c r="H631" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="632" spans="1:8">
@@ -18194,7 +18197,7 @@
         <v>59</v>
       </c>
       <c r="H633" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -18220,7 +18223,7 @@
         <v>59</v>
       </c>
       <c r="H634" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -18246,7 +18249,7 @@
         <v>59</v>
       </c>
       <c r="H635" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="636" spans="1:8">
@@ -18272,7 +18275,7 @@
         <v>59</v>
       </c>
       <c r="H636" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="637" spans="1:8">
@@ -18298,7 +18301,7 @@
         <v>59</v>
       </c>
       <c r="H637" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="638" spans="1:8">
@@ -18376,7 +18379,7 @@
         <v>59</v>
       </c>
       <c r="H640" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="641" spans="1:8">
@@ -18402,7 +18405,7 @@
         <v>59</v>
       </c>
       <c r="H641" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="642" spans="1:8">
@@ -18480,7 +18483,7 @@
         <v>59</v>
       </c>
       <c r="H644" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="645" spans="1:8">
@@ -18532,7 +18535,7 @@
         <v>59</v>
       </c>
       <c r="H646" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="647" spans="1:8">
@@ -18610,7 +18613,7 @@
         <v>59</v>
       </c>
       <c r="H649" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="650" spans="1:8">
@@ -18636,7 +18639,7 @@
         <v>59</v>
       </c>
       <c r="H650" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="651" spans="1:8">
@@ -18662,7 +18665,7 @@
         <v>59</v>
       </c>
       <c r="H651" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="652" spans="1:8">
@@ -18688,7 +18691,7 @@
         <v>59</v>
       </c>
       <c r="H652" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -18740,7 +18743,7 @@
         <v>59</v>
       </c>
       <c r="H654" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="655" spans="1:8">
@@ -18766,7 +18769,7 @@
         <v>59</v>
       </c>
       <c r="H655" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="656" spans="1:8">
@@ -18818,7 +18821,7 @@
         <v>59</v>
       </c>
       <c r="H657" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="658" spans="1:8">
@@ -18844,7 +18847,7 @@
         <v>59</v>
       </c>
       <c r="H658" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -18870,7 +18873,7 @@
         <v>59</v>
       </c>
       <c r="H659" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="660" spans="1:8">
@@ -18922,7 +18925,7 @@
         <v>59</v>
       </c>
       <c r="H661" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="662" spans="1:8">
@@ -18948,7 +18951,7 @@
         <v>59</v>
       </c>
       <c r="H662" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="663" spans="1:8">
@@ -18974,7 +18977,7 @@
         <v>59</v>
       </c>
       <c r="H663" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="664" spans="1:8">
@@ -19000,7 +19003,7 @@
         <v>59</v>
       </c>
       <c r="H664" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -19026,7 +19029,7 @@
         <v>59</v>
       </c>
       <c r="H665" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="666" spans="1:8">
@@ -19052,7 +19055,7 @@
         <v>59</v>
       </c>
       <c r="H666" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="667" spans="1:8">
@@ -19078,7 +19081,7 @@
         <v>59</v>
       </c>
       <c r="H667" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="668" spans="1:8">
@@ -19104,7 +19107,7 @@
         <v>59</v>
       </c>
       <c r="H668" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="669" spans="1:8">
@@ -19130,7 +19133,7 @@
         <v>59</v>
       </c>
       <c r="H669" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="670" spans="1:8">
@@ -19182,7 +19185,7 @@
         <v>59</v>
       </c>
       <c r="H671" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="672" spans="1:8">
@@ -19208,7 +19211,7 @@
         <v>59</v>
       </c>
       <c r="H672" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="673" spans="1:8">
@@ -19234,7 +19237,7 @@
         <v>59</v>
       </c>
       <c r="H673" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="674" spans="1:8">
@@ -19260,7 +19263,7 @@
         <v>59</v>
       </c>
       <c r="H674" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="675" spans="1:8">
@@ -19286,7 +19289,7 @@
         <v>59</v>
       </c>
       <c r="H675" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="676" spans="1:8">
@@ -19312,7 +19315,7 @@
         <v>59</v>
       </c>
       <c r="H676" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="677" spans="1:8">
@@ -19364,7 +19367,7 @@
         <v>59</v>
       </c>
       <c r="H678" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="679" spans="1:8">
@@ -19390,7 +19393,7 @@
         <v>59</v>
       </c>
       <c r="H679" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="680" spans="1:8">
@@ -19442,7 +19445,7 @@
         <v>59</v>
       </c>
       <c r="H681" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="682" spans="1:8">
@@ -19468,7 +19471,7 @@
         <v>59</v>
       </c>
       <c r="H682" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="683" spans="1:8">
@@ -19494,7 +19497,7 @@
         <v>59</v>
       </c>
       <c r="H683" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="684" spans="1:8">
@@ -19546,7 +19549,7 @@
         <v>59</v>
       </c>
       <c r="H685" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="686" spans="1:8">
@@ -19572,7 +19575,7 @@
         <v>59</v>
       </c>
       <c r="H686" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="687" spans="1:8">
@@ -19598,7 +19601,7 @@
         <v>59</v>
       </c>
       <c r="H687" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
